--- a/data/uktrains.xlsx
+++ b/data/uktrains.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Code2\1_PROJ_GROUPS\10_TrainGames\Subway Builder\Modding\subwaybuilder-uk-generic-trains\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66AD8732-D82C-48D9-B521-148044BA27B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339AC6FD-E7C1-4FEC-8272-D0102B381E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{A7C002BD-FA2E-4DBB-8D87-D5EF889110D5}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>name</t>
   </si>
@@ -138,9 +138,6 @@
     <t>roofStyle</t>
   </si>
   <si>
-    <t>bodyColor</t>
-  </si>
-  <si>
     <t>couplerWidthMultiplier</t>
   </si>
   <si>
@@ -240,30 +237,6 @@
     <t>0.8_0.79_5.8_14_1.89</t>
   </si>
   <si>
-    <t>#9da5b2</t>
-  </si>
-  <si>
-    <t>#d5dde3</t>
-  </si>
-  <si>
-    <t>#e2ebf0</t>
-  </si>
-  <si>
-    <t>#efdc87</t>
-  </si>
-  <si>
-    <t>#8b8f97</t>
-  </si>
-  <si>
-    <t>#c63b17</t>
-  </si>
-  <si>
-    <t>#db4c29</t>
-  </si>
-  <si>
-    <t>#a8afb7</t>
-  </si>
-  <si>
     <t>Small, automated metro systems built to negotiate tight urban alignments. Modeled after the Dockland Light Railway's B07 Stock.</t>
   </si>
   <si>
@@ -271,6 +244,21 @@
   </si>
   <si>
     <t>Classic DMU for lower-demand regional routes. Modeled after the Class 150 Sprinter.</t>
+  </si>
+  <si>
+    <t>#e8af10</t>
+  </si>
+  <si>
+    <t>#1e5996</t>
+  </si>
+  <si>
+    <t>#00b09c</t>
+  </si>
+  <si>
+    <t>#cf3213</t>
+  </si>
+  <si>
+    <t>#8b43cc</t>
   </si>
 </sst>
 </file>
@@ -812,6 +800,15 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF773DBD"/>
+      <color rgb="FF00AFAA"/>
+      <color rgb="FF9DA5B2"/>
+      <color rgb="FFC63B17"/>
+      <color rgb="FFFAD131"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1120,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F182819-3E12-471D-BB71-CB80EF38E747}">
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" style="2" customWidth="1"/>
@@ -1162,17 +1159,16 @@
     <col min="38" max="38" width="32.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="9.85546875" style="2" customWidth="1"/>
     <col min="40" max="40" width="9.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="11.140625" style="2" customWidth="1"/>
-    <col min="42" max="42" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="12.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="48" max="16384" width="9.28515625" style="2"/>
+    <col min="41" max="41" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="47" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,13 +1206,13 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>13</v>
@@ -1225,13 +1221,13 @@
         <v>14</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -1312,27 +1308,24 @@
         <v>40</v>
       </c>
       <c r="AU1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:49" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AV1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AW1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="E2" s="2">
         <v>4</v>
@@ -1365,7 +1358,7 @@
         <v>1.3</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P2" s="2">
         <v>1.1399999999999999</v>
@@ -1410,31 +1403,28 @@
         <v>74</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP2" s="2">
+        <v>42</v>
+      </c>
+      <c r="AO2" s="2">
         <v>0</v>
       </c>
-      <c r="AQ2" s="2" t="b">
+      <c r="AP2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="AT2" s="2" t="b">
+      <c r="AS2" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E3" s="2">
         <v>2</v>
@@ -1467,7 +1457,7 @@
         <v>1.4</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P3" s="2">
         <v>0.8</v>
@@ -1503,33 +1493,30 @@
         <v>250</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP3" s="2">
+        <v>43</v>
+      </c>
+      <c r="AO3" s="2">
         <v>1.9</v>
       </c>
-      <c r="AQ3" s="2" t="b">
+      <c r="AP3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="AT3" s="2" t="b">
+      <c r="AS3" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:50" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2">
         <v>2</v>
@@ -1562,7 +1549,7 @@
         <v>1.08</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P4" s="2">
         <v>1.03</v>
@@ -1598,33 +1585,30 @@
         <v>25</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AP4" s="2">
+        <v>43</v>
+      </c>
+      <c r="AO4" s="2">
         <v>1.9</v>
       </c>
-      <c r="AQ4" s="2" t="b">
+      <c r="AP4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AT4" s="2" t="b">
+      <c r="AS4" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:50" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2">
         <v>4</v>
@@ -1657,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P5" s="2">
         <v>0.9</v>
@@ -1684,49 +1668,48 @@
         <v>5.5</v>
       </c>
       <c r="AI5" s="2">
-        <v>600</v>
+        <v>530</v>
       </c>
       <c r="AJ5" s="2">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP5" s="2">
+        <v>43</v>
+      </c>
+      <c r="AO5" s="2">
         <v>1.3</v>
       </c>
-      <c r="AQ5" s="2" t="b">
+      <c r="AP5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AT5" s="2" t="b">
+      <c r="AS5" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="AU5" s="2">
+        <v>16</v>
+      </c>
       <c r="AV5" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AW5" s="2">
         <v>20</v>
       </c>
-      <c r="AX5" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="6" spans="1:50" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2">
         <v>2</v>
@@ -1759,7 +1742,7 @@
         <v>0.8</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P6" s="2">
         <v>0.6</v>
@@ -1792,10 +1775,10 @@
         <v>48</v>
       </c>
       <c r="AI6" s="2">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="AJ6" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AK6" s="2">
         <v>270</v>
@@ -1804,30 +1787,27 @@
         <v>280</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AN6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AO6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP6" s="2">
+        <v>42</v>
+      </c>
+      <c r="AO6" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AQ6" s="2" t="b">
+      <c r="AP6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="AT6" s="2" t="b">
+      <c r="AS6" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="AU6" s="2">
+        <v>16</v>
+      </c>
       <c r="AV6" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AW6" s="2">
-        <v>20</v>
-      </c>
-      <c r="AX6" s="2">
         <v>20</v>
       </c>
     </row>
